--- a/business_report_forms/015_seo_business_report_form--business_report_forms.xlsx
+++ b/business_report_forms/015_seo_business_report_form--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>semrush</t>
+          <t>screaming_frog</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEMrush</t>
+          <t>Screaming Frog</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>screaming_frog</t>
+          <t>bing_webmaster</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Screaming Frog</t>
+          <t>Bing Webmaster</t>
         </is>
       </c>
     </row>
@@ -1237,46 +1237,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bing_webmaster</t>
+          <t>ubers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bing Webmaster</t>
+          <t>Ubers</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>used_tools_choices</t>
+          <t>related_metrics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>moz</t>
+          <t>organic_search</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Moz</t>
+          <t>Organic Search</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>used_tools_choices</t>
+          <t>related_metrics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ubers</t>
+          <t>paid_search</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ubers</t>
+          <t>Paid Search</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>organic_search</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Organic Search</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>paid_search</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paid Search</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>display</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Display</t>
         </is>
       </c>
     </row>
@@ -1373,46 +1373,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>related_metrics_choices</t>
+          <t>competitors_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>display</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>related_metrics_choices</t>
+          <t>competitors_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>pinterest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Pinterest</t>
         </is>
       </c>
     </row>
@@ -1509,46 +1509,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>competitors_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pinterest</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>competitors_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>pinterest</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Pinterest</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -1645,44 +1645,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pinterest</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>social_media_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>social_media_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>reddit</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
